--- a/script_migration_stock_config/static/data/Recycle Receipt (stock.location).xlsx
+++ b/script_migration_stock_config/static/data/Recycle Receipt (stock.location).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/waiyan/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/waiyan/Project/Odoo/ppg/ppg/ppg/ppg/script_migration_stock_config/static/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F579A83-8BCE-C740-8ABB-3D95AC73E171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04ADBB6D-7DFE-1746-8E53-B402B35FE02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="80" yWindow="660" windowWidth="30160" windowHeight="17900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="27">
   <si>
     <t>Location Name</t>
   </si>
@@ -95,6 +95,12 @@
   </si>
   <si>
     <t>Cost of Goods Sold (Raw Recycle)</t>
+  </si>
+  <si>
+    <t>Parent Location</t>
+  </si>
+  <si>
+    <t>Virtual Locations</t>
   </si>
 </sst>
 </file>
@@ -150,11 +156,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -459,280 +468,523 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" customWidth="1"/>
-    <col min="3" max="3" width="46.6640625" customWidth="1"/>
-    <col min="4" max="4" width="44.5" customWidth="1"/>
+    <col min="1" max="2" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" customWidth="1"/>
+    <col min="4" max="4" width="46.6640625" customWidth="1"/>
+    <col min="5" max="5" width="44.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5" ht="16">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
+      <c r="B2" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
+      <c r="B4" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
+      <c r="B5" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>5</v>
+      <c r="B6" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16">
       <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>5</v>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16">
       <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16">
       <c r="A9" t="s">
         <v>4</v>
       </c>
-      <c r="B9" t="s">
-        <v>5</v>
+      <c r="B9" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16">
       <c r="A10" t="s">
         <v>4</v>
       </c>
-      <c r="B10" t="s">
-        <v>5</v>
+      <c r="B10" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16">
       <c r="A11" t="s">
         <v>4</v>
       </c>
-      <c r="B11" t="s">
-        <v>5</v>
+      <c r="B11" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16">
       <c r="A12" t="s">
         <v>4</v>
       </c>
-      <c r="B12" t="s">
-        <v>5</v>
+      <c r="B12" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16">
       <c r="A13" t="s">
         <v>4</v>
       </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="B13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16">
       <c r="A14" t="s">
         <v>4</v>
       </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16">
       <c r="A15" t="s">
         <v>4</v>
       </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="B15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16">
       <c r="A16" t="s">
         <v>4</v>
       </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="B16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16">
       <c r="A17" t="s">
         <v>4</v>
       </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="B17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16">
       <c r="A18" t="s">
         <v>4</v>
       </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="B18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16">
       <c r="A19" t="s">
         <v>4</v>
       </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="B19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="E19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="B20" s="4"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="B22" s="4"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="B26" s="4"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="B29" s="4"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="B30" s="4"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="B31" s="4"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="B32" s="4"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="4"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="4"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="4"/>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="4"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="4"/>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="4"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="4"/>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="4"/>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="4"/>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="4"/>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="4"/>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="4"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="4"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="4"/>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="4"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="4"/>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="4"/>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="4"/>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="4"/>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="4"/>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="4"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="4"/>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="4"/>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="4"/>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="4"/>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="4"/>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="4"/>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="4"/>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="4"/>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="4"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="4"/>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="4"/>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="4"/>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="4"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="4"/>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="4"/>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="4"/>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="4"/>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="4"/>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="4"/>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="4"/>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="4"/>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="4"/>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="4"/>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="4"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
